--- a/reports/Debug-purgatory-20260111/For Winter Ending (Prior Year)_Revenue.xlsx
+++ b/reports/Debug-purgatory-20260111/For Winter Ending (Prior Year)_Revenue.xlsx
@@ -124,10 +124,10 @@
     <t>T110</t>
   </si>
   <si>
+    <t>T100</t>
+  </si>
+  <si>
     <t>T105</t>
-  </si>
-  <si>
-    <t>T100</t>
   </si>
   <si>
     <t>T101</t>
@@ -659,7 +659,7 @@
         <v>41</v>
       </c>
       <c r="D4" s="2">
-        <v>8526.00</v>
+        <v>1515009.89</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -673,7 +673,7 @@
         <v>41</v>
       </c>
       <c r="D5" s="2">
-        <v>1515009.89</v>
+        <v>8526.00</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -694,26 +694,26 @@
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>39</v>
-      </c>
+      <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
         <v>41</v>
       </c>
       <c r="D7" s="2">
-        <v>945.30</v>
+        <v>1263.50</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="2"/>
+      <c r="B8" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="C8" s="2" t="s">
         <v>41</v>
       </c>
       <c r="D8" s="2">
-        <v>1263.50</v>
+        <v>945.30</v>
       </c>
     </row>
     <row r="9" spans="1:4">
